--- a/Assets/Data/Commodore/C64/250407/Data C64 250407 v2.0.0.xlsx
+++ b/Assets/Data/Commodore/C64/250407/Data C64 250407 v2.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\Commodore\C64\250407\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\Commodore\C64\250407\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99199C1-1294-412E-B1DA-101F5EBDDA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46519D04-5AA5-420C-B61D-F4C94EA4D4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14989" uniqueCount="4126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14995" uniqueCount="4129">
   <si>
     <r>
       <t xml:space="preserve"># Hardware: </t>
@@ -12503,6 +12503,24 @@
     <t>Generic shared files/Component local files/TIP29A.pdf</t>
   </si>
   <si>
+    <t>Forum64; Repair Corner (primarily German)</t>
+  </si>
+  <si>
+    <t>https://www.forum64.de/index.php?board/183-repair-corner/</t>
+  </si>
+  <si>
+    <t>064b6d58-37cc-4a4c-af89-56e97d04b155</t>
+  </si>
+  <si>
+    <t>Zimmers; Character ROMs</t>
+  </si>
+  <si>
+    <t>https://www.zimmers.net/anonftp/pub/cbm/firmware/characters/</t>
+  </si>
+  <si>
+    <t>378da1be-0eea-45e9-9bd1-89b7ddc0e8a2</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -12514,17 +12532,8 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2026-May-12</t>
+      <t>2026-June-10</t>
     </r>
-  </si>
-  <si>
-    <t>Forum64; Repair Corner (primarily German)</t>
-  </si>
-  <si>
-    <t>https://www.forum64.de/index.php?board/183-repair-corner/</t>
-  </si>
-  <si>
-    <t>064b6d58-37cc-4a4c-af89-56e97d04b155</t>
   </si>
 </sst>
 </file>
@@ -13187,7 +13196,7 @@
     </row>
     <row r="3" spans="1:10" s="11" customFormat="1" ht="21">
       <c r="A3" s="11" t="s">
-        <v>4122</v>
+        <v>4128</v>
       </c>
       <c r="I3"/>
     </row>
@@ -13291,7 +13300,12 @@
         <v>0.3</v>
       </c>
       <c r="E10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="F10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="7">
+        <v>1</v>
+      </c>
       <c r="H10" s="7"/>
       <c r="I10" t="s">
         <v>13</v>
@@ -13311,7 +13325,12 @@
         <v>0.3</v>
       </c>
       <c r="E11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="F11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="7">
+        <v>1</v>
+      </c>
       <c r="H11" s="7"/>
       <c r="I11" t="s">
         <v>15</v>
@@ -16176,7 +16195,7 @@
         <v>413</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>349</v>
@@ -18826,7 +18845,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -69722,7 +69741,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9014B11-7294-4050-ABF4-8B4EFBD7F103}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -69821,46 +69840,46 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>373</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2749</v>
-      </c>
-      <c r="C12" t="s">
-        <v>2750</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2751</v>
+    <row r="12" spans="1:4" s="44" customFormat="1">
+      <c r="A12" s="43" t="s">
+        <v>363</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>4125</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>4126</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>4127</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>411</v>
+        <v>373</v>
       </c>
       <c r="B13" t="s">
-        <v>2752</v>
+        <v>2749</v>
       </c>
       <c r="C13" t="s">
-        <v>2753</v>
+        <v>2750</v>
       </c>
       <c r="D13" t="s">
-        <v>2754</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B14" t="s">
-        <v>2755</v>
+        <v>2752</v>
       </c>
       <c r="C14" t="s">
-        <v>2756</v>
+        <v>2753</v>
       </c>
       <c r="D14" t="s">
-        <v>2757</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -69868,68 +69887,79 @@
         <v>420</v>
       </c>
       <c r="B15" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2757</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>420</v>
+      </c>
+      <c r="B16" t="s">
         <v>2758</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>2759</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>2760</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="44" customFormat="1">
-      <c r="A16" s="44" t="s">
+    <row r="17" spans="1:4" s="44" customFormat="1">
+      <c r="A17" s="44" t="s">
         <v>552</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B17" s="44" t="s">
         <v>2761</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C17" s="44" t="s">
         <v>2762</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="D17" s="44" t="s">
         <v>2763</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="22"/>
-    </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="25"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="D21" s="1"/>
+      <c r="A18" s="22"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="25"/>
     </row>
     <row r="22" spans="1:4">
       <c r="D22" s="1"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="23"/>
       <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:4">
+      <c r="A24" s="23"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="23"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="24"/>
+    <row r="25" spans="1:4">
+      <c r="D25" s="1"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="23"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="12"/>
-    </row>
-    <row r="38" spans="4:4">
-      <c r="D38" s="57"/>
-    </row>
-    <row r="40" spans="4:4">
-      <c r="D40" s="57"/>
-    </row>
-    <row r="53" spans="4:4">
-      <c r="D53" s="6"/>
-    </row>
-    <row r="59" spans="4:4">
-      <c r="D59" s="1"/>
+      <c r="A31" s="24"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="12"/>
+    </row>
+    <row r="39" spans="4:4">
+      <c r="D39" s="57"/>
+    </row>
+    <row r="41" spans="4:4">
+      <c r="D41" s="57"/>
+    </row>
+    <row r="54" spans="4:4">
+      <c r="D54" s="6"/>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="1"/>
@@ -69942,6 +69972,9 @@
     </row>
     <row r="63" spans="4:4">
       <c r="D63" s="1"/>
+    </row>
+    <row r="64" spans="4:4">
+      <c r="D64" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -70460,13 +70493,13 @@
         <v>2830</v>
       </c>
       <c r="B25" t="s">
+        <v>4122</v>
+      </c>
+      <c r="C25" t="s">
         <v>4123</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>4124</v>
-      </c>
-      <c r="D25" t="s">
-        <v>4125</v>
       </c>
     </row>
     <row r="26" spans="1:4">
